--- a/backend/data/products.xlsx
+++ b/backend/data/products.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,41 +431,9 @@
         <v>updatedAt</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>3b610272-606d-4a05-a654-bd22d6633166</v>
-      </c>
-      <c r="B2" t="str">
-        <v>candy biscuit</v>
-      </c>
-      <c r="C2" t="str">
-        <v>these are very tasty candy biscuits gay as hell</v>
-      </c>
-      <c r="D2">
-        <v>40</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="str">
-        <v>["/uploads/products/images/1790623968745-WhatsApp-Image-2026-09-18-at-7.53.49-AM.jpeg","/uploads/products/images/1790623968751-WhatsApp-Image-2026-09-19-at-3.45.16-AM.jpeg"]</v>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v>Home</v>
-      </c>
-      <c r="I2" t="str">
-        <v>2026-09-28T19:32:48.763Z</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2026-09-29T09:53:05.477Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
   </ignoredErrors>
 </worksheet>
 </file>